--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136875899</v>
+        <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>79233</v>
+        <v>83463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421511</v>
+        <v>421450</v>
       </c>
       <c r="R3" t="n">
-        <v>6961892</v>
+        <v>6961994</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -861,6 +864,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,16 +882,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136875899</t>
+          <t>https://artportalen.se/Sighting/136875998</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136875925</v>
+        <v>136875899</v>
       </c>
       <c r="B4" t="n">
-        <v>80095</v>
+        <v>79233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421526</v>
+        <v>421511</v>
       </c>
       <c r="R4" t="n">
-        <v>6961896</v>
+        <v>6961892</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -980,16 +984,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136875925</t>
+          <t>https://artportalen.se/Sighting/136875899</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136876019</v>
+        <v>136875925</v>
       </c>
       <c r="B5" t="n">
-        <v>58008</v>
+        <v>80095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,39 +1001,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421451</v>
+        <v>421526</v>
       </c>
       <c r="R5" t="n">
-        <v>6961996</v>
+        <v>6961896</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1064,11 +1063,6 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1092,48 +1086,44 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136876019</t>
+          <t>https://artportalen.se/Sighting/136875925</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136875963</v>
+        <v>136876019</v>
       </c>
       <c r="B6" t="n">
-        <v>57195</v>
+        <v>58008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1142,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421449</v>
+        <v>421451</v>
       </c>
       <c r="R6" t="n">
-        <v>6961952</v>
+        <v>6961996</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1182,7 +1172,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Uppskrämd</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,51 +1198,60 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136875963</t>
+          <t>https://artportalen.se/Sighting/136876019</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136875986</v>
+        <v>136875963</v>
       </c>
       <c r="B7" t="n">
-        <v>58112</v>
+        <v>57195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421448</v>
+        <v>421449</v>
       </c>
       <c r="R7" t="n">
-        <v>6961988</v>
+        <v>6961952</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,6 +1286,11 @@
           <t>2026-09-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Uppskrämd</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1309,6 +1313,108 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136875963</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136875986</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>421448</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6961988</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136875986</t>
         </is>
@@ -1322,6 +1428,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875913</v>
       </c>
       <c r="B2" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136875899</v>
       </c>
       <c r="B4" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136875925</v>
       </c>
       <c r="B5" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875913</v>
       </c>
       <c r="B2" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136875899</v>
       </c>
       <c r="B4" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136875925</v>
       </c>
       <c r="B5" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875913</v>
       </c>
       <c r="B2" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136875899</v>
       </c>
       <c r="B4" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136875925</v>
       </c>
       <c r="B5" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875913</v>
       </c>
       <c r="B2" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136875899</v>
       </c>
       <c r="B4" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136875925</v>
       </c>
       <c r="B5" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875913</v>
       </c>
       <c r="B2" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136875899</v>
       </c>
       <c r="B4" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136875925</v>
       </c>
       <c r="B5" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875913</v>
       </c>
       <c r="B2" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136875899</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136875925</v>
       </c>
       <c r="B5" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136876019</v>
       </c>
       <c r="B6" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>136875963</v>
       </c>
       <c r="B7" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136875986</v>
       </c>
       <c r="B8" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875913</v>
       </c>
       <c r="B2" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136875899</v>
       </c>
       <c r="B4" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136875925</v>
       </c>
       <c r="B5" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136876019</v>
       </c>
       <c r="B6" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>136875963</v>
       </c>
       <c r="B7" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136875986</v>
       </c>
       <c r="B8" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -1121,11 +1121,7 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
@@ -1237,11 +1233,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875913</v>
       </c>
       <c r="B2" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136875899</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136875925</v>
       </c>
       <c r="B5" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136876019</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>136875963</v>
       </c>
       <c r="B7" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>136875986</v>
       </c>
       <c r="B8" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875913</v>
       </c>
       <c r="B2" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136875899</v>
       </c>
       <c r="B4" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136875925</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136876019</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>136875963</v>
       </c>
       <c r="B7" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>136875986</v>
       </c>
       <c r="B8" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875913</v>
       </c>
       <c r="B2" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136875899</v>
       </c>
       <c r="B4" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136875925</v>
       </c>
       <c r="B5" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136876019</v>
       </c>
       <c r="B6" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>136875986</v>
       </c>
       <c r="B8" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875913</v>
       </c>
       <c r="B2" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136875899</v>
       </c>
       <c r="B4" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136875925</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875913</v>
       </c>
       <c r="B2" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136875899</v>
       </c>
       <c r="B4" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136875925</v>
       </c>
       <c r="B5" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2025 artfynd.xlsx
+++ b/artfynd/A 50435-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136875998</v>
       </c>
       <c r="B3" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
